--- a/outputs/scenario_output.xlsx
+++ b/outputs/scenario_output.xlsx
@@ -17,6 +17,9 @@
     <sheet name="Emissions BAU" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Emissions Low Carbon" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Emissions High Growth" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Supply BAU" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Supply Low Carbon" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Supply High Growth" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -120,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -159,9 +162,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -529,14 +529,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -557,7 +557,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>397.81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6"/>
@@ -592,271 +592,80 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>360</v>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Demand (PJ)</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>37.5</v>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>0</v>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Fuel</t>
-        </is>
-      </c>
+      <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Demand (PJ)</t>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Electricity</t>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Residential</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>117.53</v>
+        <v>12</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Natural Gas</t>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>95.73</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Oil Products</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>94.54000000000001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Renewables</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>18.01</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Coal</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr"/>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Natural Gas</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Oil Products</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Renewables</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Coal</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>117.53</v>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>95.73</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>94.54000000000001</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>72</v>
+        <v>12</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -900,7 +709,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -932,13 +741,13 @@
         <v>2022</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>19.1115</v>
+        <v>0.4488</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>18.0003</v>
+        <v>1.8379</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>37.1118</v>
+        <v>2.2867</v>
       </c>
     </row>
     <row r="7">
@@ -946,13 +755,13 @@
         <v>2023</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>19.9745</v>
+        <v>0.4699</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>18.8214</v>
+        <v>1.9244</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>38.7959</v>
+        <v>2.3943</v>
       </c>
     </row>
     <row r="8">
@@ -960,13 +769,13 @@
         <v>2024</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>20.8772</v>
+        <v>0.4921</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>19.6805</v>
+        <v>2.015</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>40.5577</v>
+        <v>2.5071</v>
       </c>
     </row>
     <row r="9">
@@ -974,13 +783,13 @@
         <v>2025</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>21.8215</v>
+        <v>0.5152</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>20.5794</v>
+        <v>2.1099</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>42.4009</v>
+        <v>2.6251</v>
       </c>
     </row>
     <row r="10">
@@ -988,13 +797,13 @@
         <v>2026</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>22.8093</v>
+        <v>0.5395</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>21.52</v>
+        <v>2.2093</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>44.3293</v>
+        <v>2.7488</v>
       </c>
     </row>
     <row r="11">
@@ -1002,13 +811,13 @@
         <v>2027</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>23.8426</v>
+        <v>0.5649</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>22.5041</v>
+        <v>2.3133</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>46.3467</v>
+        <v>2.8782</v>
       </c>
     </row>
     <row r="12">
@@ -1016,13 +825,13 @@
         <v>2028</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>24.9236</v>
+        <v>0.5915</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>23.534</v>
+        <v>2.4222</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>48.4576</v>
+        <v>3.0137</v>
       </c>
     </row>
     <row r="13">
@@ -1030,13 +839,13 @@
         <v>2029</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>26.0545</v>
+        <v>0.6193</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>24.6115</v>
+        <v>2.5363</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>50.666</v>
+        <v>3.1556</v>
       </c>
     </row>
     <row r="14">
@@ -1044,13 +853,13 @@
         <v>2030</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>27.2375</v>
+        <v>0.6485</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>25.7392</v>
+        <v>2.6557</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>52.9767</v>
+        <v>3.3042</v>
       </c>
     </row>
     <row r="15">
@@ -1058,13 +867,13 @@
         <v>2031</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>28.4752</v>
+        <v>0.679</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>26.9191</v>
+        <v>2.7808</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>55.3943</v>
+        <v>3.4598</v>
       </c>
     </row>
     <row r="16">
@@ -1072,13 +881,13 @@
         <v>2032</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>29.7701</v>
+        <v>0.711</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>28.1539</v>
+        <v>2.9117</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>57.924</v>
+        <v>3.6227</v>
       </c>
     </row>
     <row r="17">
@@ -1086,13 +895,13 @@
         <v>2033</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>31.1248</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>29.446</v>
+        <v>3.0488</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>60.5708</v>
+        <v>3.7933</v>
       </c>
     </row>
     <row r="18">
@@ -1100,13 +909,13 @@
         <v>2034</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>32.5421</v>
+        <v>0.7796</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>30.7982</v>
+        <v>3.1924</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>63.3403</v>
+        <v>3.972</v>
       </c>
     </row>
     <row r="19">
@@ -1114,13 +923,13 @@
         <v>2035</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>34.0251</v>
+        <v>0.8163</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>32.2132</v>
+        <v>3.3427</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>66.2383</v>
+        <v>4.159</v>
       </c>
     </row>
     <row r="20">
@@ -1128,13 +937,13 @@
         <v>2036</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>35.5766</v>
+        <v>0.8547</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>33.694</v>
+        <v>3.5001</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>69.2706</v>
+        <v>4.3548</v>
       </c>
     </row>
     <row r="21">
@@ -1142,13 +951,13 @@
         <v>2037</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>37.2</v>
+        <v>0.8949</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>35.2438</v>
+        <v>3.6649</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>72.4438</v>
+        <v>4.5598</v>
       </c>
     </row>
     <row r="22">
@@ -1156,13 +965,13 @@
         <v>2038</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>38.8985</v>
+        <v>0.9371</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>36.8656</v>
+        <v>3.8375</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>75.7641</v>
+        <v>4.7746</v>
       </c>
     </row>
     <row r="23">
@@ -1170,13 +979,13 @@
         <v>2039</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>40.6758</v>
+        <v>0.9812</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>38.5629</v>
+        <v>4.0182</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>79.23869999999999</v>
+        <v>4.9994</v>
       </c>
     </row>
     <row r="24">
@@ -1184,13 +993,13 @@
         <v>2040</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>42.5354</v>
+        <v>1.0274</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>40.3393</v>
+        <v>4.2074</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>82.8747</v>
+        <v>5.2348</v>
       </c>
     </row>
     <row r="25">
@@ -1198,13 +1007,13 @@
         <v>2041</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>44.4813</v>
+        <v>1.0758</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>42.1984</v>
+        <v>4.4055</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>86.6797</v>
+        <v>5.4813</v>
       </c>
     </row>
     <row r="26">
@@ -1212,13 +1021,13 @@
         <v>2042</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>46.5174</v>
+        <v>1.1265</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>44.1441</v>
+        <v>4.6129</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>90.6615</v>
+        <v>5.7394</v>
       </c>
     </row>
     <row r="27">
@@ -1226,13 +1035,13 @@
         <v>2043</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>48.648</v>
+        <v>1.1795</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>46.1805</v>
+        <v>4.8302</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>94.82850000000001</v>
+        <v>6.0097</v>
       </c>
     </row>
     <row r="28">
@@ -1240,13 +1049,13 @@
         <v>2044</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>50.8775</v>
+        <v>1.235</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>48.3118</v>
+        <v>5.0576</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>99.1893</v>
+        <v>6.2926</v>
       </c>
     </row>
     <row r="29">
@@ -1254,13 +1063,13 @@
         <v>2045</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>53.2105</v>
+        <v>1.2932</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>50.5425</v>
+        <v>5.2957</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>103.753</v>
+        <v>6.5889</v>
       </c>
     </row>
     <row r="30">
@@ -1268,13 +1077,13 @@
         <v>2046</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>55.6519</v>
+        <v>1.3541</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>52.8772</v>
+        <v>5.5451</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>108.5291</v>
+        <v>6.8992</v>
       </c>
     </row>
     <row r="31">
@@ -1282,13 +1091,13 @@
         <v>2047</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>58.2067</v>
+        <v>1.4178</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>55.3209</v>
+        <v>5.8062</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>113.5276</v>
+        <v>7.224</v>
       </c>
     </row>
     <row r="32">
@@ -1296,13 +1105,13 @@
         <v>2048</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>60.8803</v>
+        <v>1.4846</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>57.8786</v>
+        <v>6.0796</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>118.7589</v>
+        <v>7.5642</v>
       </c>
     </row>
     <row r="33">
@@ -1310,13 +1119,13 @@
         <v>2049</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>63.6782</v>
+        <v>1.5545</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>60.5556</v>
+        <v>6.3659</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>124.2338</v>
+        <v>7.9204</v>
       </c>
     </row>
     <row r="34">
@@ -1324,13 +1133,13 @@
         <v>2050</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>66.6062</v>
+        <v>1.6277</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>63.3577</v>
+        <v>6.6656</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>129.9639</v>
+        <v>8.2933</v>
       </c>
     </row>
     <row r="35">
@@ -1338,13 +1147,13 @@
         <v>2051</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>69.6705</v>
+        <v>1.7044</v>
       </c>
       <c r="C35" s="9" t="n">
-        <v>66.29049999999999</v>
+        <v>6.9795</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>135.961</v>
+        <v>8.6839</v>
       </c>
     </row>
     <row r="36">
@@ -1352,19 +1161,2416 @@
         <v>2052</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>72.87730000000001</v>
+        <v>1.7846</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>69.3604</v>
+        <v>7.3082</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>142.2377</v>
+        <v>9.0928</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Supply &amp; Transformation — BAU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Electricity generation requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Generated: 2026-03-08 22:45:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Electricity Demand (PJ)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Gross Generation (PJ)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>T&amp;D Losses (PJ)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Primary Energy Input (PJ)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Efficiency (%)</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Loss Rate (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>47.06</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>49.89</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>51.37</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>52.89</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>54.45</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>56.06</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>57.72</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>59.43</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>2046</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n">
+        <v>2047</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>77.27</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>79.56</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
+        <v>2049</v>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>81.92</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>2050</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>84.34</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>2051</v>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>2052</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Supply &amp; Transformation — Low Carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Electricity generation requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Generated: 2026-03-08 22:45:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Electricity Demand (PJ)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Gross Generation (PJ)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>T&amp;D Losses (PJ)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Primary Energy Input (PJ)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Efficiency (%)</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Loss Rate (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>37.63</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>38.35</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>40.62</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>43.03</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>43.86</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>46.01</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>2046</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n">
+        <v>2047</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>47.81</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
+        <v>2049</v>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>2050</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>15.69</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>2051</v>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>2052</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Supply &amp; Transformation — High Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Electricity generation requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Generated: 2026-03-08 22:45:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Electricity Demand (PJ)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Gross Generation (PJ)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>T&amp;D Losses (PJ)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Primary Energy Input (PJ)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Efficiency (%)</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Loss Rate (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>40.86</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>46.91</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>64.73</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>67.78</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>70.97</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>26.01</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>74.31</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>77.81</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>85.31</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>89.33</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>93.54000000000001</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>97.94</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>35.89</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>34.58</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>2046</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>112.44</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n">
+        <v>2047</v>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>117.73</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>43.15</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>123.28</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
+        <v>2049</v>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>129.08</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>2050</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>135.16</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>2051</v>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>141.52</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>2052</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>51.87</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>148.19</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1376,7 +3582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1404,7 +3610,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -1437,7 +3643,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Business as Usual — continuation of current trends</t>
+          <t>Uploaded baseline growth assumptions</t>
         </is>
       </c>
     </row>
@@ -1461,428 +3667,188 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Annual Intensity Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Low Carbon</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Low Carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Uploaded low-carbon case</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Annual Growth Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Residential</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
         <v>0.025</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>0.035</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Annual Intensity Change</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Residential</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
-        <v>-0.005</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>-0.008</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="n">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n">
-        <v>-0.005</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="n">
-        <v>-0.005</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Low Carbon</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="B23" s="15" t="n">
+        <v>-0.015</v>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>High Growth</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Low Carbon</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>High Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Aggressive decarbonization with efficiency and renewables</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Uploaded high-growth case</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Annual Growth Rate</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Residential</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Annual Intensity Change</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Residential</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>-0.025</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n">
-        <v>-0.015</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="n">
-        <v>-0.025</v>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>High Growth</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>High Growth</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Rapid economic expansion with moderate efficiency gains</t>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>Annual Growth Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n">
-        <v>0.035</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="n">
-        <v>0.045</v>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Annual Intensity Change</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>Residential</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="n">
-        <v>-0.008</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-      <c r="B55" s="15" t="n">
-        <v>-0.012</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="n">
-        <v>-0.008</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="B57" s="15" t="n">
-        <v>-0.008</v>
+      <c r="B33" s="15" t="n">
+        <v>-0.0075</v>
       </c>
     </row>
   </sheetData>
@@ -1900,15 +3866,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1921,14 +3885,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Business as Usual — continuation of current trends</t>
+          <t>Uploaded baseline growth assumptions</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -1940,7 +3904,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>397.81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -1950,7 +3914,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>922.73</v>
+        <v>47.98</v>
       </c>
     </row>
     <row r="7">
@@ -1961,7 +3925,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -1977,45 +3941,13 @@
           <t>Residential</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
         <v>2022</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -2023,19 +3955,7 @@
         <v>2027</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>416.53</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>40.38</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>0</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="12">
@@ -2043,19 +3963,7 @@
         <v>2032</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>481.93</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="13">
@@ -2063,19 +3971,7 @@
         <v>2037</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>557.61</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>46.81</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0</v>
+        <v>30.98</v>
       </c>
     </row>
     <row r="14">
@@ -2083,19 +3979,7 @@
         <v>2042</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>645.17</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>50.41</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>35.84</v>
       </c>
     </row>
     <row r="15">
@@ -2103,19 +3987,7 @@
         <v>2047</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>746.48</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>54.28</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>0</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="16">
@@ -2123,19 +3995,7 @@
         <v>2052</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>863.6900000000001</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>47.98</v>
       </c>
     </row>
     <row r="17"/>
@@ -2155,40 +4015,16 @@
           <t>Natural Gas</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Oil Products</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Renewables</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Coal</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
         <v>2022</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>117.53</v>
+        <v>12</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>95.73</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>94.54000000000001</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -2196,19 +4032,10 @@
         <v>2027</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>135.22</v>
+        <v>13.88</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>110.3</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>107.58</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>20.84</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>83.31</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="21">
@@ -2216,19 +4043,10 @@
         <v>2032</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>155.64</v>
+        <v>16.06</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>127.13</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>122.53</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>24.11</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>96.39</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="22">
@@ -2236,19 +4054,10 @@
         <v>2037</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>179.2</v>
+        <v>18.59</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>146.57</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>139.67</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>27.89</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>111.52</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="23">
@@ -2256,19 +4065,10 @@
         <v>2042</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>206.39</v>
+        <v>21.51</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>169.01</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>159.34</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>32.27</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>129.03</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="24">
@@ -2276,19 +4076,10 @@
         <v>2047</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>237.78</v>
+        <v>24.88</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>194.94</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>181.93</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>37.34</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>149.3</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="25">
@@ -2296,25 +4087,16 @@
         <v>2052</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>274.02</v>
+        <v>28.79</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>224.89</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>207.88</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>172.74</v>
+        <v>19.19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2326,15 +4108,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2347,14 +4127,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aggressive decarbonization with efficiency and renewables</t>
+          <t>Uploaded low-carbon case</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -2366,7 +4146,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>397.81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -2376,7 +4156,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>387.97</v>
+        <v>26.66</v>
       </c>
     </row>
     <row r="7">
@@ -2387,7 +4167,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -2403,45 +4183,13 @@
           <t>Residential</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
         <v>2022</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -2449,19 +4197,7 @@
         <v>2027</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>358.38</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>37.46</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>0</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="12">
@@ -2469,19 +4205,7 @@
         <v>2032</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>356.77</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>37.42</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>22.01</v>
       </c>
     </row>
     <row r="13">
@@ -2489,19 +4213,7 @@
         <v>2037</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>355.17</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>37.37</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="14">
@@ -2509,19 +4221,7 @@
         <v>2042</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>353.58</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>37.33</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="15">
@@ -2529,19 +4229,7 @@
         <v>2047</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>351.99</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>0</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="16">
@@ -2549,19 +4237,7 @@
         <v>2052</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>350.41</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>37.25</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>26.66</v>
       </c>
     </row>
     <row r="17"/>
@@ -2581,40 +4257,16 @@
           <t>Natural Gas</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Oil Products</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Renewables</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Coal</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
         <v>2022</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>117.53</v>
+        <v>12</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>95.73</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>94.54000000000001</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -2622,19 +4274,10 @@
         <v>2027</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>110.27</v>
+        <v>12.59</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>89.65000000000001</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>89.65000000000001</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>39.45</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>67.12</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2642,19 +4285,10 @@
         <v>2032</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>103.08</v>
+        <v>13.21</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>83.63</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>60.71</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>62.29</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2662,19 +4296,10 @@
         <v>2037</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>95.94</v>
+        <v>13.85</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>77.66</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>81.78</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>57.49</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="23">
@@ -2682,19 +4307,10 @@
         <v>2042</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>88.86</v>
+        <v>14.53</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>71.73</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>75.22</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>102.67</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>52.74</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="24">
@@ -2702,19 +4318,10 @@
         <v>2047</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>81.84999999999999</v>
+        <v>15.25</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>65.86</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>70.48</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>123.39</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>48.02</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="25">
@@ -2722,25 +4329,16 @@
         <v>2052</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>74.88</v>
+        <v>15.99</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>60.03</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>65.79000000000001</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>143.93</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>43.34</v>
+        <v>10.66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2752,15 +4350,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2773,14 +4369,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapid economic expansion with moderate efficiency gains</t>
+          <t>Uploaded high-growth case</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -2792,7 +4388,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>397.81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -2802,7 +4398,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1522.85</v>
+        <v>79.53</v>
       </c>
     </row>
     <row r="7">
@@ -2813,7 +4409,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>4.71%</t>
         </is>
       </c>
     </row>
@@ -2829,45 +4425,13 @@
           <t>Residential</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
         <v>2022</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>360</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -2875,19 +4439,7 @@
         <v>2027</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>453.54</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>42.78</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>0</v>
+        <v>25.17</v>
       </c>
     </row>
     <row r="12">
@@ -2895,19 +4447,7 @@
         <v>2032</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>571.39</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>48.81</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0</v>
+        <v>31.69</v>
       </c>
     </row>
     <row r="13">
@@ -2915,19 +4455,7 @@
         <v>2037</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>719.85</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>55.69</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="14">
@@ -2935,19 +4463,7 @@
         <v>2042</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>906.9</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>63.54</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="15">
@@ -2955,19 +4471,7 @@
         <v>2047</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>1142.54</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>0</v>
+        <v>63.18</v>
       </c>
     </row>
     <row r="16">
@@ -2975,19 +4479,7 @@
         <v>2052</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>1439.42</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>82.72</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>79.53</v>
       </c>
     </row>
     <row r="17"/>
@@ -3007,40 +4499,16 @@
           <t>Natural Gas</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Oil Products</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Renewables</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Coal</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
         <v>2022</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>117.53</v>
+        <v>12</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>95.73</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>94.54000000000001</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>18.01</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -3048,19 +4516,10 @@
         <v>2027</v>
       </c>
       <c r="B20" s="9" t="n">
-        <v>146.93</v>
+        <v>15.1</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>119.92</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>116.43</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>22.69</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>90.70999999999999</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="21">
@@ -3068,19 +4527,10 @@
         <v>2032</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>183.82</v>
+        <v>19.01</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>150.3</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>143.62</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>28.58</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>114.28</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="22">
@@ -3088,19 +4538,10 @@
         <v>2037</v>
       </c>
       <c r="B22" s="9" t="n">
-        <v>230.12</v>
+        <v>23.93</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>188.47</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>177.45</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>36.01</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>143.97</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="23">
@@ -3108,19 +4549,10 @@
         <v>2042</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>288.23</v>
+        <v>30.12</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>236.43</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>219.58</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>181.38</v>
+        <v>20.08</v>
       </c>
     </row>
     <row r="24">
@@ -3128,19 +4560,10 @@
         <v>2047</v>
       </c>
       <c r="B24" s="9" t="n">
-        <v>361.2</v>
+        <v>37.91</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>296.71</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>272.09</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>57.15</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>228.51</v>
+        <v>25.27</v>
       </c>
     </row>
     <row r="25">
@@ -3148,25 +4571,16 @@
         <v>2052</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>452.87</v>
+        <v>47.72</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>372.5</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>337.61</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>71.98999999999999</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>287.88</v>
+        <v>31.81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3197,7 +4611,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -3229,13 +4643,13 @@
         <v>2022</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>397.81</v>
+        <v>20</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>397.81</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>397.81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -3243,13 +4657,13 @@
         <v>2027</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>457.25</v>
+        <v>23.14</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>396.15</v>
+        <v>20.98</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>496.68</v>
+        <v>25.17</v>
       </c>
     </row>
     <row r="7">
@@ -3257,13 +4671,13 @@
         <v>2032</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>525.8</v>
+        <v>26.77</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>394.5</v>
+        <v>22.01</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>620.61</v>
+        <v>31.69</v>
       </c>
     </row>
     <row r="8">
@@ -3271,13 +4685,13 @@
         <v>2037</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>604.85</v>
+        <v>30.98</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>392.86</v>
+        <v>23.09</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>776.01</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="9">
@@ -3285,13 +4699,13 @@
         <v>2042</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>696.05</v>
+        <v>35.84</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>391.22</v>
+        <v>24.22</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>970.98</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="10">
@@ -3299,13 +4713,13 @@
         <v>2047</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>801.29</v>
+        <v>41.47</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>389.59</v>
+        <v>25.41</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1215.66</v>
+        <v>63.18</v>
       </c>
     </row>
     <row r="11">
@@ -3313,13 +4727,13 @@
         <v>2052</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>922.73</v>
+        <v>47.98</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>387.97</v>
+        <v>26.66</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1522.85</v>
+        <v>79.53</v>
       </c>
     </row>
   </sheetData>
@@ -3355,7 +4769,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -3387,13 +4801,13 @@
         <v>2022</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>37.11</v>
+        <v>2.29</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>37.11</v>
+        <v>2.29</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>37.11</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="6">
@@ -3401,13 +4815,13 @@
         <v>2027</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>42.66</v>
+        <v>2.65</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>34.84</v>
+        <v>2.4</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>46.35</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="7">
@@ -3415,13 +4829,13 @@
         <v>2032</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>49.07</v>
+        <v>3.06</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>32.59</v>
+        <v>2.52</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>57.92</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="8">
@@ -3429,13 +4843,13 @@
         <v>2037</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>56.46</v>
+        <v>3.54</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>30.35</v>
+        <v>2.64</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>72.44</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="9">
@@ -3443,13 +4857,13 @@
         <v>2042</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>64.98</v>
+        <v>4.1</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>28.14</v>
+        <v>2.77</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>90.66</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="10">
@@ -3457,13 +4871,13 @@
         <v>2047</v>
       </c>
       <c r="B10" s="9" t="n">
-        <v>74.81</v>
+        <v>4.74</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>25.94</v>
+        <v>2.91</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>113.53</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="11">
@@ -3471,13 +4885,13 @@
         <v>2052</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>86.16</v>
+        <v>5.49</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>23.76</v>
+        <v>3.05</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>142.24</v>
+        <v>9.09</v>
       </c>
     </row>
   </sheetData>
@@ -3520,7 +4934,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -3552,13 +4966,13 @@
         <v>2022</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>19.1115</v>
+        <v>0.4488</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>18.0003</v>
+        <v>1.8379</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>37.1118</v>
+        <v>2.2867</v>
       </c>
     </row>
     <row r="7">
@@ -3566,13 +4980,13 @@
         <v>2023</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>19.6482</v>
+        <v>0.4621</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>18.5118</v>
+        <v>1.8923</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>38.16</v>
+        <v>2.3544</v>
       </c>
     </row>
     <row r="8">
@@ -3580,13 +4994,13 @@
         <v>2024</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>20.2004</v>
+        <v>0.4758</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>19.0382</v>
+        <v>1.9483</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>39.2386</v>
+        <v>2.4241</v>
       </c>
     </row>
     <row r="9">
@@ -3594,13 +5008,13 @@
         <v>2025</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>20.7685</v>
+        <v>0.4898</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>19.5798</v>
+        <v>2.006</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>40.3483</v>
+        <v>2.4958</v>
       </c>
     </row>
     <row r="10">
@@ -3608,13 +5022,13 @@
         <v>2026</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>21.353</v>
+        <v>0.5043</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>20.1371</v>
+        <v>2.0653</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>41.4901</v>
+        <v>2.5696</v>
       </c>
     </row>
     <row r="11">
@@ -3622,13 +5036,13 @@
         <v>2027</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>21.9543</v>
+        <v>0.5193</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>20.7106</v>
+        <v>2.1265</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>42.6649</v>
+        <v>2.6458</v>
       </c>
     </row>
     <row r="12">
@@ -3636,13 +5050,13 @@
         <v>2028</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>22.573</v>
+        <v>0.5346</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>21.3007</v>
+        <v>2.1894</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>43.8737</v>
+        <v>2.724</v>
       </c>
     </row>
     <row r="13">
@@ -3650,13 +5064,13 @@
         <v>2029</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>23.2095</v>
+        <v>0.5505</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>21.908</v>
+        <v>2.2542</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>45.1175</v>
+        <v>2.8047</v>
       </c>
     </row>
     <row r="14">
@@ -3664,13 +5078,13 @@
         <v>2030</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>23.8644</v>
+        <v>0.5668</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>22.5328</v>
+        <v>2.321</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>46.3972</v>
+        <v>2.8878</v>
       </c>
     </row>
     <row r="15">
@@ -3678,13 +5092,13 @@
         <v>2031</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>24.5382</v>
+        <v>0.5835</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>23.1759</v>
+        <v>2.3897</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>47.7141</v>
+        <v>2.9732</v>
       </c>
     </row>
     <row r="16">
@@ -3692,13 +5106,13 @@
         <v>2032</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>25.2315</v>
+        <v>0.6008</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>23.8375</v>
+        <v>2.4604</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>49.069</v>
+        <v>3.0612</v>
       </c>
     </row>
     <row r="17">
@@ -3706,13 +5120,13 @@
         <v>2033</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>25.9447</v>
+        <v>0.6186</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>24.5185</v>
+        <v>2.5332</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>50.4632</v>
+        <v>3.1518</v>
       </c>
     </row>
     <row r="18">
@@ -3720,13 +5134,13 @@
         <v>2034</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>26.6786</v>
+        <v>0.6369</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>25.2192</v>
+        <v>2.6082</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>51.8978</v>
+        <v>3.2451</v>
       </c>
     </row>
     <row r="19">
@@ -3734,13 +5148,13 @@
         <v>2035</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>27.4337</v>
+        <v>0.6558</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>25.9402</v>
+        <v>2.6854</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>53.3739</v>
+        <v>3.3412</v>
       </c>
     </row>
     <row r="20">
@@ -3748,13 +5162,13 @@
         <v>2036</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>28.2107</v>
+        <v>0.6752</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>26.6823</v>
+        <v>2.7649</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>54.893</v>
+        <v>3.4401</v>
       </c>
     </row>
     <row r="21">
@@ -3762,13 +5176,13 @@
         <v>2037</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>29.0101</v>
+        <v>0.6952</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>27.4459</v>
+        <v>2.8467</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>56.456</v>
+        <v>3.5419</v>
       </c>
     </row>
     <row r="22">
@@ -3776,13 +5190,13 @@
         <v>2038</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>29.8326</v>
+        <v>0.7157</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>28.2317</v>
+        <v>2.931</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>58.0643</v>
+        <v>3.6467</v>
       </c>
     </row>
     <row r="23">
@@ -3790,13 +5204,13 @@
         <v>2039</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>30.679</v>
+        <v>0.7369</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>29.0404</v>
+        <v>3.0178</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>59.7194</v>
+        <v>3.7547</v>
       </c>
     </row>
     <row r="24">
@@ -3804,13 +5218,13 @@
         <v>2040</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>31.5499</v>
+        <v>0.7587</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>29.8726</v>
+        <v>3.1071</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>61.4225</v>
+        <v>3.8658</v>
       </c>
     </row>
     <row r="25">
@@ -3818,13 +5232,13 @@
         <v>2041</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>32.4459</v>
+        <v>0.7812</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>30.729</v>
+        <v>3.199</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>63.1749</v>
+        <v>3.9802</v>
       </c>
     </row>
     <row r="26">
@@ -3832,13 +5246,13 @@
         <v>2042</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>33.368</v>
+        <v>0.8043</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>31.6104</v>
+        <v>3.2937</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>64.97839999999999</v>
+        <v>4.098</v>
       </c>
     </row>
     <row r="27">
@@ -3846,13 +5260,13 @@
         <v>2043</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>34.3167</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>32.5174</v>
+        <v>3.3912</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>66.83410000000001</v>
+        <v>4.2193</v>
       </c>
     </row>
     <row r="28">
@@ -3860,13 +5274,13 @@
         <v>2044</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>35.293</v>
+        <v>0.8526</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>33.4509</v>
+        <v>3.4916</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>68.7439</v>
+        <v>4.3442</v>
       </c>
     </row>
     <row r="29">
@@ -3874,13 +5288,13 @@
         <v>2045</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>36.2976</v>
+        <v>0.8779</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>34.4115</v>
+        <v>3.595</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>70.70910000000001</v>
+        <v>4.4729</v>
       </c>
     </row>
     <row r="30">
@@ -3888,13 +5302,13 @@
         <v>2046</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>37.3313</v>
+        <v>0.9039</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>35.4002</v>
+        <v>3.7014</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>72.7315</v>
+        <v>4.6053</v>
       </c>
     </row>
     <row r="31">
@@ -3902,13 +5316,13 @@
         <v>2047</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>38.395</v>
+        <v>0.9306</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>36.4177</v>
+        <v>3.8109</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>74.81270000000001</v>
+        <v>4.7415</v>
       </c>
     </row>
     <row r="32">
@@ -3916,13 +5330,13 @@
         <v>2048</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>39.4896</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>37.4648</v>
+        <v>3.9237</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>76.95440000000001</v>
+        <v>4.8819</v>
       </c>
     </row>
     <row r="33">
@@ -3930,13 +5344,13 @@
         <v>2049</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>40.6159</v>
+        <v>0.9865</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>38.5425</v>
+        <v>4.0399</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>79.1584</v>
+        <v>5.0264</v>
       </c>
     </row>
     <row r="34">
@@ -3944,13 +5358,13 @@
         <v>2050</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>41.775</v>
+        <v>1.0157</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>39.6516</v>
+        <v>4.1595</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>81.42659999999999</v>
+        <v>5.1752</v>
       </c>
     </row>
     <row r="35">
@@ -3958,13 +5372,13 @@
         <v>2051</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>42.9677</v>
+        <v>1.0458</v>
       </c>
       <c r="C35" s="9" t="n">
-        <v>40.793</v>
+        <v>4.2826</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>83.7607</v>
+        <v>5.3284</v>
       </c>
     </row>
     <row r="36">
@@ -3972,13 +5386,13 @@
         <v>2052</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>44.195</v>
+        <v>1.0767</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>41.9678</v>
+        <v>4.4093</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>86.1628</v>
+        <v>5.486</v>
       </c>
     </row>
   </sheetData>
@@ -4022,7 +5436,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:15:53</t>
+          <t>Generated: 2026-03-08 22:45:01</t>
         </is>
       </c>
     </row>
@@ -4054,13 +5468,13 @@
         <v>2022</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>19.1115</v>
+        <v>0.4488</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>18.0003</v>
+        <v>1.8379</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>37.1118</v>
+        <v>2.2867</v>
       </c>
     </row>
     <row r="7">
@@ -4068,13 +5482,13 @@
         <v>2023</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>18.8786</v>
+        <v>0.4531</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>17.7773</v>
+        <v>1.8556</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>36.6559</v>
+        <v>2.3087</v>
       </c>
     </row>
     <row r="8">
@@ -4082,13 +5496,13 @@
         <v>2024</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>18.646</v>
+        <v>0.4575</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>17.5546</v>
+        <v>1.8734</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>36.2006</v>
+        <v>2.3309</v>
       </c>
     </row>
     <row r="9">
@@ -4096,13 +5510,13 @@
         <v>2025</v>
       </c>
       <c r="B9" s="9" t="n">
-        <v>18.4139</v>
+        <v>0.4619</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>17.3323</v>
+        <v>1.8915</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>35.7462</v>
+        <v>2.3534</v>
       </c>
     </row>
     <row r="10">
@@ -4110,13 +5524,13 @@
         <v>2026</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>18.1822</v>
+        <v>0.4663</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17.1104</v>
+        <v>1.9097</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>35.2926</v>
+        <v>2.376</v>
       </c>
     </row>
     <row r="11">
@@ -4124,13 +5538,13 @@
         <v>2027</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>17.9508</v>
+        <v>0.4708</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>16.8889</v>
+        <v>1.9281</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>34.8397</v>
+        <v>2.3989</v>
       </c>
     </row>
     <row r="12">
@@ -4138,13 +5552,13 @@
         <v>2028</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>17.7198</v>
+        <v>0.4753</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>16.6677</v>
+        <v>1.9466</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>34.3875</v>
+        <v>2.4219</v>
       </c>
     </row>
     <row r="13">
@@ -4152,13 +5566,13 @@
         <v>2029</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>17.4893</v>
+        <v>0.4799</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>16.4469</v>
+        <v>1.9653</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>33.9362</v>
+        <v>2.4452</v>
       </c>
     </row>
     <row r="14">
@@ -4166,13 +5580,13 @@
         <v>2030</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>17.2591</v>
+        <v>0.4845</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>16.2265</v>
+        <v>1.9843</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>33.4856</v>
+        <v>2.4688</v>
       </c>
     </row>
     <row r="15">
@@ -4180,13 +5594,13 @@
         <v>2031</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>17.0293</v>
+        <v>0.4892</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>16.0064</v>
+        <v>2.0034</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>33.0357</v>
+        <v>2.4926</v>
       </c>
     </row>
     <row r="16">
@@ -4194,13 +5608,13 @@
         <v>2032</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>16.7998</v>
+        <v>0.4939</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>15.7868</v>
+        <v>2.0226</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>32.5866</v>
+        <v>2.5165</v>
       </c>
     </row>
     <row r="17">
@@ -4208,13 +5622,13 @@
         <v>2033</v>
       </c>
       <c r="B17" s="9" t="n">
-        <v>16.5708</v>
+        <v>0.4987</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>15.5675</v>
+        <v>2.0421</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>32.1383</v>
+        <v>2.5408</v>
       </c>
     </row>
     <row r="18">
@@ -4222,13 +5636,13 @@
         <v>2034</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>16.3421</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>15.3485</v>
+        <v>2.0618</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>31.6906</v>
+        <v>2.5653</v>
       </c>
     </row>
     <row r="19">
@@ -4236,13 +5650,13 @@
         <v>2035</v>
       </c>
       <c r="B19" s="9" t="n">
-        <v>16.1138</v>
+        <v>0.5083</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>15.1299</v>
+        <v>2.0816</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>31.2437</v>
+        <v>2.5899</v>
       </c>
     </row>
     <row r="20">
@@ -4250,13 +5664,13 @@
         <v>2036</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>15.8859</v>
+        <v>0.5132</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>14.9117</v>
+        <v>2.1016</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>30.7976</v>
+        <v>2.6148</v>
       </c>
     </row>
     <row r="21">
@@ -4264,13 +5678,13 @@
         <v>2037</v>
       </c>
       <c r="B21" s="9" t="n">
-        <v>15.6584</v>
+        <v>0.5181</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>14.6939</v>
+        <v>2.1219</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>30.3523</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="22">
@@ -4278,13 +5692,13 @@
         <v>2038</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>15.4313</v>
+        <v>0.5231</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>14.4764</v>
+        <v>2.1423</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>29.9077</v>
+        <v>2.6654</v>
       </c>
     </row>
     <row r="23">
@@ -4292,13 +5706,13 @@
         <v>2039</v>
       </c>
       <c r="B23" s="9" t="n">
-        <v>15.2045</v>
+        <v>0.5282</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>14.2593</v>
+        <v>2.1629</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>29.4638</v>
+        <v>2.6911</v>
       </c>
     </row>
     <row r="24">
@@ -4306,13 +5720,13 @@
         <v>2040</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>14.9781</v>
+        <v>0.5333</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>14.0425</v>
+        <v>2.1837</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>29.0206</v>
+        <v>2.717</v>
       </c>
     </row>
     <row r="25">
@@ -4320,13 +5734,13 @@
         <v>2041</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>14.7521</v>
+        <v>0.5384</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>13.8261</v>
+        <v>2.2048</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>28.5782</v>
+        <v>2.7432</v>
       </c>
     </row>
     <row r="26">
@@ -4334,13 +5748,13 @@
         <v>2042</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>14.5264</v>
+        <v>0.5436</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>13.6101</v>
+        <v>2.226</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>28.1365</v>
+        <v>2.7696</v>
       </c>
     </row>
     <row r="27">
@@ -4348,13 +5762,13 @@
         <v>2043</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>14.3011</v>
+        <v>0.5488</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>13.3944</v>
+        <v>2.2474</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>27.6955</v>
+        <v>2.7962</v>
       </c>
     </row>
     <row r="28">
@@ -4362,13 +5776,13 @@
         <v>2044</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>14.0762</v>
+        <v>0.5541</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>13.1791</v>
+        <v>2.269</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>27.2553</v>
+        <v>2.8231</v>
       </c>
     </row>
     <row r="29">
@@ -4376,13 +5790,13 @@
         <v>2045</v>
       </c>
       <c r="B29" s="9" t="n">
-        <v>13.8517</v>
+        <v>0.5594</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>12.9641</v>
+        <v>2.2909</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>26.8158</v>
+        <v>2.8503</v>
       </c>
     </row>
     <row r="30">
@@ -4390,13 +5804,13 @@
         <v>2046</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>13.6275</v>
+        <v>0.5648</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>12.7495</v>
+        <v>2.3129</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>26.377</v>
+        <v>2.8777</v>
       </c>
     </row>
     <row r="31">
@@ -4404,13 +5818,13 @@
         <v>2047</v>
       </c>
       <c r="B31" s="9" t="n">
-        <v>13.4037</v>
+        <v>0.5702</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>12.5352</v>
+        <v>2.3352</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>25.9389</v>
+        <v>2.9054</v>
       </c>
     </row>
     <row r="32">
@@ -4418,13 +5832,13 @@
         <v>2048</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>13.1803</v>
+        <v>0.5757</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>12.3213</v>
+        <v>2.3577</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>25.5016</v>
+        <v>2.9334</v>
       </c>
     </row>
     <row r="33">
@@ -4432,13 +5846,13 @@
         <v>2049</v>
       </c>
       <c r="B33" s="9" t="n">
-        <v>12.9572</v>
+        <v>0.5813</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>12.1078</v>
+        <v>2.3804</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>25.065</v>
+        <v>2.9617</v>
       </c>
     </row>
     <row r="34">
@@ -4446,13 +5860,13 @@
         <v>2050</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>12.7345</v>
+        <v>0.5869</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>11.8945</v>
+        <v>2.4033</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>24.629</v>
+        <v>2.9902</v>
       </c>
     </row>
     <row r="35">
@@ -4460,13 +5874,13 @@
         <v>2051</v>
       </c>
       <c r="B35" s="9" t="n">
-        <v>12.5121</v>
+        <v>0.5925</v>
       </c>
       <c r="C35" s="9" t="n">
-        <v>11.6817</v>
+        <v>2.4264</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>24.1938</v>
+        <v>3.0189</v>
       </c>
     </row>
     <row r="36">
@@ -4474,13 +5888,13 @@
         <v>2052</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>12.2901</v>
+        <v>0.5982</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>11.4692</v>
+        <v>2.4497</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>23.7593</v>
+        <v>3.0479</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/scenario_output.xlsx
+++ b/outputs/scenario_output.xlsx
@@ -557,7 +557,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 22:45:01</t>
+          <t>Generated: 2026-03-08 23:08:10</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_output.xlsx
+++ b/outputs/scenario_output.xlsx
@@ -557,7 +557,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:08:10</t>
+          <t>Generated: 2026-03-08 23:10:45</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_output.xlsx
+++ b/outputs/scenario_output.xlsx
@@ -557,7 +557,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:10:45</t>
+          <t>Generated: 2026-03-08 23:24:34</t>
         </is>
       </c>
     </row>

--- a/outputs/scenario_output.xlsx
+++ b/outputs/scenario_output.xlsx
@@ -557,7 +557,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-08 23:24:34</t>
+          <t>Generated: 2026-03-08 23:36:12</t>
         </is>
       </c>
     </row>
